--- a/01_analyses_states/Maharashtra/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Maharashtra/results/SoIB_summaries.xlsx
@@ -509,10 +509,10 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -520,16 +520,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="E3">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -537,16 +537,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
       <c r="E4">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -557,13 +557,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="E5">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -577,10 +577,10 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="E6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -591,7 +591,7 @@
         <v>63</v>
       </c>
       <c r="C7">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C8">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +750,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,7 +764,7 @@
         <v>249</v>
       </c>
       <c r="C4">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2">
-        <v>70.8</v>
+        <v>71</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>79.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>20.2</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
